--- a/docs/import-templates/matieres_exemple.xlsx
+++ b/docs/import-templates/matieres_exemple.xlsx
@@ -1,49 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Donnees" sheetId="1" r:id="rId1"/>
-    <sheet name="Mode d emploi" sheetId="2" r:id="rId2"/>
-    <sheet name="Exemples" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Donnees" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Mode d emploi" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Exemples" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Nom (anglais)</t>
+  </si>
+  <si>
+    <t>Nom (arabe)</t>
+  </si>
+  <si>
+    <t>Libellé court</t>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>Français</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>LANGUES</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Physique-Chimie</t>
+  </si>
+  <si>
+    <t>Physics-Chemistry</t>
+  </si>
+  <si>
+    <t>SCIENCES</t>
+  </si>
+  <si>
+    <t>SVT</t>
+  </si>
+  <si>
+    <t>Sciences de la vie et de la Terre</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>Histoire-Géographie</t>
+  </si>
+  <si>
+    <t>SCIENCES_SOCIALES</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>Éducation physique et sportive</t>
+  </si>
+  <si>
+    <t>SPORTS</t>
+  </si>
+  <si>
+    <t>Colonne</t>
+  </si>
+  <si>
+    <t>Requis</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Requis. Ex. MATH.</t>
+  </si>
+  <si>
+    <t>Requis. Nom affiché de la matière.</t>
+  </si>
+  <si>
+    <t>Optionnel.</t>
+  </si>
+  <si>
+    <t>Requis. LANGUES, SCIENCES, MATHEMATIQUES, SCIENCES_SOCIALES, ARTS, SPORTS ou AUTRE.</t>
+  </si>
+  <si>
+    <t>Remarques</t>
+  </si>
+  <si>
+    <t>- Ne modifiez pas la premiere ligne : elle contient les en-tetes.</t>
+  </si>
+  <si>
+    <t>- Ajoutez une ligne par personne a partir de la ligne 2 ; les lignes vides sont ignorees.</t>
+  </si>
+  <si>
+    <t>- Les dates s'ecrivent JJ/MM/AAAA (ex. 14/03/2012) ou AAAA-MM-JJ (ex. 2012-03-14).</t>
+  </si>
+  <si>
+    <t>- Sexe : M, F ou AUTRE.</t>
+  </si>
+  <si>
+    <t>- Code : optionnel. Laisses vide, un code est genere automatiquement.</t>
+  </si>
+  <si>
+    <t>- Un code utilise deux fois dans le fichier (ou deja present dans l'ecole) est refuse.</t>
+  </si>
+  <si>
+    <t>- Ligne d'exemple : voir la feuille « Exemples » (non importee).</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,13 +160,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,290 +499,266 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="1" max="6" width="18.857142857142858" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Code</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Nom (anglais)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Nom (arabe)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Libellé court</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Catégorie</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>MATH</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Mathématiques</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Mathematics</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Maths</v>
-      </c>
-      <c r="F2" t="str">
-        <v>MATHEMATIQUES</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>FR</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Français</v>
-      </c>
-      <c r="C3" t="str">
-        <v>French</v>
-      </c>
-      <c r="F3" t="str">
-        <v>LANGUES</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PC</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Physique-Chimie</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Physics-Chemistry</v>
-      </c>
-      <c r="F4" t="str">
-        <v>SCIENCES</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SVT</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Sciences de la vie et de la Terre</v>
-      </c>
-      <c r="F5" t="str">
-        <v>SCIENCES</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>HG</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Histoire-Géographie</v>
-      </c>
-      <c r="F6" t="str">
-        <v>SCIENCES_SOCIALES</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>EPS</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Éducation physique et sportive</v>
-      </c>
-      <c r="F7" t="str">
-        <v>SPORTS</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="90.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.857142857142858" customWidth="1"/>
+    <col min="2" max="2" width="10.857142857142858" customWidth="1"/>
+    <col min="3" max="3" width="42.142857142857146" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Colonne</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Requis</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Code</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Requis. Ex. MATH.</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Requis. Ex. MATH.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Requis. Nom affiché de la matière.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Requis. Nom affiché de la matière.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Nom (anglais)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Optionnel.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Optionnel.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Nom (arabe)</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Optionnel.</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Optionnel.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Libellé court</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Optionnel.</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Optionnel.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Catégorie</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Requis. LANGUES, SCIENCES, MATHEMATIQUES, SCIENCES_SOCIALES, ARTS, SPORTS ou AUTRE.</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Requis. LANGUES, SCIENCES, MATHEMATIQUES, SCIENCES_SOCIALES, ARTS, SPORTS ou AUTRE.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Remarques</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>- Ne modifiez pas la premiere ligne : elle contient les en-tetes.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>- Ajoutez une ligne par personne a partir de la ligne 2 ; les lignes vides sont ignorees.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>- Les dates s'ecrivent JJ/MM/AAAA (ex. 14/03/2012) ou AAAA-MM-JJ (ex. 2012-03-14).</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>- Sexe : M, F ou AUTRE.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>- Code : optionnel. Laisses vide, un code est genere automatiquement.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>- Un code utilise deux fois dans le fichier (ou deja present dans l'ecole) est refuse.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>- Ligne d'exemple : voir la feuille « Exemples » (non importee).</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="1" max="6" width="18.857142857142858" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Code</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Nom (anglais)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Nom (arabe)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Libellé court</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Catégorie</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/docs/import-templates/matieres_exemple.xlsx
+++ b/docs/import-templates/matieres_exemple.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>Code</t>
   </si>
@@ -79,6 +79,18 @@
   </si>
   <si>
     <t>SPORTS</t>
+  </si>
+  <si>
+    <t>MATH</t>
+  </si>
+  <si>
+    <t>Mathématiques</t>
+  </si>
+  <si>
+    <t>mathematics</t>
+  </si>
+  <si>
+    <t>Math</t>
   </si>
   <si>
     <t>Colonne</t>
@@ -500,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="6" width="18.857142857142858" customWidth="1"/>
@@ -537,6 +549,9 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
@@ -551,6 +566,9 @@
       <c r="C3" t="s">
         <v>12</v>
       </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
@@ -562,6 +580,9 @@
       <c r="B4" t="s">
         <v>15</v>
       </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
@@ -573,6 +594,9 @@
       <c r="B5" t="s">
         <v>17</v>
       </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
@@ -584,8 +608,28 @@
       <c r="B6" t="s">
         <v>20</v>
       </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
       <c r="F6" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -607,13 +651,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +665,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +676,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +687,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +698,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +709,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,50 +720,50 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
